--- a/corr_matrix/residual_exam4B_3PL.xlsx
+++ b/corr_matrix/residual_exam4B_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>4B02</t>
@@ -560,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.08462308561110897</v>
+        <v>-0.08464638624489307</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.24486429240346</v>
+        <v>-0.2448676460450449</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03403998459968107</v>
+        <v>-0.03403167644075569</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07980658539218041</v>
+        <v>0.07985375352306696</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.03744605237173713</v>
+        <v>-0.03744488905136631</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1999997122227498</v>
+        <v>-0.200009584203924</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0977185886527058</v>
+        <v>-0.09766639528079774</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1329808928859596</v>
+        <v>-0.1329755888981897</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.06299827245447812</v>
+        <v>-0.06301555941258484</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1615650345081366</v>
+        <v>-0.1615219396448177</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09729986073630169</v>
+        <v>0.09729447794028562</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1518668796056647</v>
+        <v>-0.151890049394269</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1370001908077368</v>
+        <v>-0.1370110932267852</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1127249739367101</v>
+        <v>-0.1127447276196937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1301134543407329</v>
+        <v>0.1301420301288289</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.08926044237724363</v>
+        <v>-0.08928327343374871</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.04342727593843259</v>
+        <v>-0.04343917371057757</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01761125922990024</v>
+        <v>0.01761412623434595</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.04085644152611399</v>
+        <v>-0.04085686309296784</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1888581676898567</v>
+        <v>-0.188867102039792</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05467102820091285</v>
+        <v>0.0547162421167379</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007725553553551071</v>
+        <v>0.007719108417908815</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1230522628003109</v>
+        <v>0.1229848088942521</v>
       </c>
     </row>
     <row r="3">
@@ -636,76 +641,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.08462308561110897</v>
+        <v>-0.08464638624489307</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.251350982309115</v>
+        <v>0.2513619141247522</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03388860138772199</v>
+        <v>0.03389474866447097</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2024791682856258</v>
+        <v>-0.2024303536628317</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09396301647531208</v>
+        <v>0.09397025379957963</v>
       </c>
       <c r="H3" t="n">
-        <v>0.147260629518228</v>
+        <v>0.1472532516336906</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01892050678490932</v>
+        <v>-0.01899579525744688</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.05741738910501687</v>
+        <v>-0.05741092997065441</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.007233252805239102</v>
+        <v>-0.007230268214835463</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2037796074009404</v>
+        <v>-0.2037246405950557</v>
       </c>
       <c r="M3" t="n">
-        <v>0.136307629311697</v>
+        <v>0.1363094251330516</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05861628963390444</v>
+        <v>0.05861398777211479</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0992366786064435</v>
+        <v>-0.09923430316579242</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0442752239474057</v>
+        <v>-0.04427799258094919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1363284743839978</v>
+        <v>-0.136338510416104</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1769782150924639</v>
+        <v>-0.1769622594398686</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1183335022482099</v>
+        <v>-0.1183397601942636</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1615178162577572</v>
+        <v>-0.1615079074050299</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2053558100523721</v>
+        <v>-0.205344913828722</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1845230968966702</v>
+        <v>-0.1845197060142055</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01539907032880599</v>
+        <v>-0.01538861344301527</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1838508178307589</v>
+        <v>-0.1838604016574403</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03781351473814417</v>
+        <v>0.03782327476348226</v>
       </c>
     </row>
     <row r="4">
@@ -715,76 +720,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.24486429240346</v>
+        <v>-0.2448676460450449</v>
       </c>
       <c r="C4" t="n">
-        <v>0.251350982309115</v>
+        <v>0.2513619141247522</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1641743968276844</v>
+        <v>-0.1641880662763804</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.04197946165434764</v>
+        <v>-0.0419943084139904</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07152400367609392</v>
+        <v>0.07151687431741016</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08415698998235678</v>
+        <v>-0.08415953032468541</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1352642931227452</v>
+        <v>0.1352361207220975</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1636980813644023</v>
+        <v>-0.1637199028819743</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1114101201624133</v>
+        <v>0.1114063568288674</v>
       </c>
       <c r="L4" t="n">
-        <v>0.183832121812959</v>
+        <v>0.1838359289957879</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2301923548361527</v>
+        <v>-0.2301907554757129</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01006264811439499</v>
+        <v>-0.01005988316810668</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2534047094186642</v>
+        <v>-0.2534064549677817</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008223609492324712</v>
+        <v>0.008226347996079523</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2027761353082572</v>
+        <v>-0.2027822939357506</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1105162447999311</v>
+        <v>-0.1104974025953657</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04130627747294239</v>
+        <v>-0.04130761654237346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07230634013522975</v>
+        <v>0.07228881108610685</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1526331017759159</v>
+        <v>0.1526276934181151</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.105976736817143</v>
+        <v>-0.1059820257557489</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.06855846166913156</v>
+        <v>-0.06858664143690414</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2041591103366696</v>
+        <v>-0.2041538565607109</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002591875264624667</v>
+        <v>0.002594116113053682</v>
       </c>
     </row>
     <row r="5">
@@ -794,76 +799,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.03403998459968107</v>
+        <v>-0.03403167644075569</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03388860138772199</v>
+        <v>0.03389474866447097</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1641743968276844</v>
+        <v>-0.1641880662763804</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01712533607872593</v>
+        <v>-0.01713410957800912</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0831354948246171</v>
+        <v>-0.0831426441443486</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04254705141842782</v>
+        <v>0.04253296836890524</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07099217309295078</v>
+        <v>0.07098112814343835</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1805506351140071</v>
+        <v>-0.1805711626398838</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1892000947944167</v>
+        <v>-0.1892058977549604</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03105045137921373</v>
+        <v>0.03104911175054685</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3020615274634627</v>
+        <v>0.3020738477862308</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1878904927738786</v>
+        <v>-0.187892504626183</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02851201803101562</v>
+        <v>-0.02851547724628593</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1427816322610606</v>
+        <v>-0.1427839111183754</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.100999249391847</v>
+        <v>0.1009985120149051</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1704423847705924</v>
+        <v>0.1704531742841626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1147181727134604</v>
+        <v>0.1147158543249246</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07158893700517846</v>
+        <v>0.07157572414790149</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1484353574178925</v>
+        <v>-0.1484329545327224</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09317167190127962</v>
+        <v>0.09316943816964515</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1759719034724505</v>
+        <v>-0.1759882940074698</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1550708141127509</v>
+        <v>0.1550830387321695</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3926531288297701</v>
+        <v>-0.392647984146043</v>
       </c>
     </row>
     <row r="6">
@@ -873,76 +878,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07980658539218041</v>
+        <v>0.07985375352306696</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2024791682856258</v>
+        <v>-0.2024303536628317</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.04197946165434764</v>
+        <v>-0.0419943084139904</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01712533607872593</v>
+        <v>-0.01713410957800912</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1882162239023616</v>
+        <v>-0.188224769685078</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2871613869799375</v>
+        <v>-0.2871624316725024</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04132357457580654</v>
+        <v>-0.04145949892369828</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2526458512181832</v>
+        <v>-0.2526631089712042</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0517026777190949</v>
+        <v>0.05170641173022021</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0665623972148628</v>
+        <v>0.06658816866465489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07576258559381105</v>
+        <v>-0.07575694681038168</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1054425165922538</v>
+        <v>-0.1054358383379895</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1195781180097518</v>
+        <v>-0.1195813813797366</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.06896020041471466</v>
+        <v>-0.06895002916103123</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1689145242965955</v>
+        <v>-0.168918636599317</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.05169378760910826</v>
+        <v>-0.05165913851231753</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07135766496733724</v>
+        <v>0.07136432734008905</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3523985602249988</v>
+        <v>0.3523852192916541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09505737554166228</v>
+        <v>0.0950624669854571</v>
       </c>
       <c r="V6" t="n">
-        <v>0.118968576666418</v>
+        <v>0.1189671756449346</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01036291193966002</v>
+        <v>0.0103739633050346</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00548367558091848</v>
+        <v>0.005500447295324173</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1604492106734625</v>
+        <v>0.1604558452863722</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +957,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.03744605237173713</v>
+        <v>-0.03744488905136631</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09396301647531208</v>
+        <v>0.09397025379957963</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07152400367609392</v>
+        <v>0.07151687431741016</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0831354948246171</v>
+        <v>-0.0831426441443486</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1882162239023616</v>
+        <v>-0.188224769685078</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03413999649054054</v>
+        <v>-0.03413993551830318</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1168243958062176</v>
+        <v>0.1167991068772435</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.07215275751263256</v>
+        <v>-0.0721658427839616</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2454740949700095</v>
+        <v>-0.2454794389239447</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.09732673408191664</v>
+        <v>-0.0973208981158154</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2151317993322903</v>
+        <v>0.2151386237058797</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3374254556157044</v>
+        <v>0.3374241891805202</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1658199945466683</v>
+        <v>-0.1658147609980652</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08146122736654089</v>
+        <v>0.08146038707765331</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02924199543938287</v>
+        <v>0.02923796604566015</v>
       </c>
       <c r="R7" t="n">
-        <v>0.05114826993789341</v>
+        <v>0.05116121844796447</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.238209463478683</v>
+        <v>-0.2382071290449189</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.02334607088535038</v>
+        <v>-0.02336016640614961</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2337481338195899</v>
+        <v>-0.2337564123759923</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3460520810595338</v>
+        <v>-0.3460556248487562</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05793189048947804</v>
+        <v>0.05790932504450037</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2665605611139177</v>
+        <v>-0.2665557023588059</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0122884121285944</v>
+        <v>-0.0122854438104707</v>
       </c>
     </row>
     <row r="8">
@@ -1031,76 +1036,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1999997122227498</v>
+        <v>-0.200009584203924</v>
       </c>
       <c r="C8" t="n">
-        <v>0.147260629518228</v>
+        <v>0.1472532516336906</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08415698998235678</v>
+        <v>-0.08415953032468541</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04254705141842782</v>
+        <v>0.04253296836890524</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2871613869799375</v>
+        <v>-0.2871624316725024</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03413999649054054</v>
+        <v>-0.03413993551830318</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1126403639790113</v>
+        <v>-0.1126208784777905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4857024224618787</v>
+        <v>0.4857022504580917</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06140691624638508</v>
+        <v>0.06140512089895213</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1220195494236948</v>
+        <v>-0.1220237238600751</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1809675678978812</v>
+        <v>-0.180955477384502</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04163723932424038</v>
+        <v>0.04163734380550961</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2432501582110838</v>
+        <v>0.2432517924539264</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0753458375272324</v>
+        <v>0.07534464190533968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1044094678235964</v>
+        <v>-0.1044111446358953</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02157707434981406</v>
+        <v>-0.02157389823051373</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06670647932390059</v>
+        <v>0.06670616488106976</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1334749252320553</v>
+        <v>-0.1334810332232283</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08165012022830004</v>
+        <v>-0.081643276467966</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0913861053480238</v>
+        <v>-0.0913860628590379</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.07622998685931839</v>
+        <v>-0.07623953495036964</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2121528262135174</v>
+        <v>-0.2121464427935643</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.1278732479702974</v>
+        <v>-0.12786554682743</v>
       </c>
     </row>
     <row r="9">
@@ -1110,76 +1115,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.0977185886527058</v>
+        <v>-0.09766639528079774</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01892050678490932</v>
+        <v>-0.01899579525744688</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1352642931227452</v>
+        <v>0.1352361207220975</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07099217309295078</v>
+        <v>0.07098112814343835</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.04132357457580654</v>
+        <v>-0.04145949892369828</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1168243958062176</v>
+        <v>0.1167991068772435</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1126403639790113</v>
+        <v>-0.1126208784777905</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.203469041679722</v>
+        <v>-0.203403225488153</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2997470565357468</v>
+        <v>-0.2996817048881829</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.08872733390121922</v>
+        <v>-0.08893462975776294</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01292427003830488</v>
+        <v>0.01291673102192414</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05564155752038005</v>
+        <v>-0.05566163582415517</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2298759365661213</v>
+        <v>-0.2298199330257334</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05289203578750189</v>
+        <v>0.05285579173705504</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.09073050659398031</v>
+        <v>-0.09065038121514975</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1180822078952703</v>
+        <v>-0.1181941949370826</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03783608070598626</v>
+        <v>0.03780226506787893</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03356070501395225</v>
+        <v>0.0335619272526978</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08331930945958867</v>
+        <v>-0.08330327777706209</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02216035478439437</v>
+        <v>-0.0221554387693413</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06151757704249376</v>
+        <v>0.0615875120513269</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0380965087930407</v>
+        <v>0.03809097619133221</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2242213227618077</v>
+        <v>-0.2241990516037803</v>
       </c>
     </row>
     <row r="10">
@@ -1189,76 +1194,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1329808928859596</v>
+        <v>-0.1329755888981897</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.05741738910501687</v>
+        <v>-0.05741092997065441</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1636980813644023</v>
+        <v>-0.1637199028819743</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1805506351140071</v>
+        <v>-0.1805711626398838</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2526458512181832</v>
+        <v>-0.2526631089712042</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07215275751263256</v>
+        <v>-0.0721658427839616</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4857024224618787</v>
+        <v>0.4857022504580917</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.203469041679722</v>
+        <v>-0.203403225488153</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0975129409499888</v>
+        <v>0.09750105203880292</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3159227162870309</v>
+        <v>-0.3159181032107848</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3956042339504994</v>
+        <v>-0.3956048494952887</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09444000546418722</v>
+        <v>0.09443214469808967</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4246943292662151</v>
+        <v>0.4246869187218706</v>
       </c>
       <c r="P10" t="n">
-        <v>0.123211647511375</v>
+        <v>0.1232043876901009</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1014756375578282</v>
+        <v>0.1014743213336673</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1796124706958087</v>
+        <v>-0.1796024334445058</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.05038977099940693</v>
+        <v>-0.05039009457823163</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2492698718688146</v>
+        <v>-0.2493001100699632</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1604137612389836</v>
+        <v>0.1604078606574873</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.004585028316468048</v>
+        <v>-0.004598423223231451</v>
       </c>
       <c r="W10" t="n">
-        <v>0.08578769030793169</v>
+        <v>0.08577628200945127</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04108519734879935</v>
+        <v>0.04108595376632146</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.06856156683471989</v>
+        <v>-0.06855543635369574</v>
       </c>
     </row>
     <row r="11">
@@ -1268,76 +1273,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.06299827245447812</v>
+        <v>-0.06301555941258484</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.007233252805239102</v>
+        <v>-0.007230268214835463</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1114101201624133</v>
+        <v>0.1114063568288674</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1892000947944167</v>
+        <v>-0.1892058977549604</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0517026777190949</v>
+        <v>0.05170641173022021</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2454740949700095</v>
+        <v>-0.2454794389239447</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06140691624638508</v>
+        <v>0.06140512089895213</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2997470565357468</v>
+        <v>-0.2996817048881829</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0975129409499888</v>
+        <v>0.09750105203880292</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05008601830270702</v>
+        <v>0.05010500319727119</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3268533308202196</v>
+        <v>-0.3268549561522535</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2044342402161325</v>
+        <v>-0.2044226052390355</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1075178628469187</v>
+        <v>0.1075175694010564</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0128007419277695</v>
+        <v>-0.01278997784750327</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.00179411739675652</v>
+        <v>0.001787335441895209</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1376237063138007</v>
+        <v>-0.1375966078458671</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.09544975381223193</v>
+        <v>-0.09545010646903414</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1737983313306898</v>
+        <v>0.1737964549322871</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09095571445045993</v>
+        <v>0.09095292335246596</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1983526812488879</v>
+        <v>0.1983530599286313</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01388558215828179</v>
+        <v>-0.01391138176242628</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1849044782988844</v>
+        <v>-0.1849012636303527</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.03808703406425892</v>
+        <v>-0.03808508483684496</v>
       </c>
     </row>
     <row r="12">
@@ -1347,76 +1352,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1615650345081366</v>
+        <v>-0.1615219396448177</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2037796074009404</v>
+        <v>-0.2037246405950557</v>
       </c>
       <c r="D12" t="n">
-        <v>0.183832121812959</v>
+        <v>0.1838359289957879</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03105045137921373</v>
+        <v>0.03104911175054685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0665623972148628</v>
+        <v>0.06658816866465489</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09732673408191664</v>
+        <v>-0.0973208981158154</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1220195494236948</v>
+        <v>-0.1220237238600751</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08872733390121922</v>
+        <v>-0.08893462975776294</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3159227162870309</v>
+        <v>-0.3159181032107848</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05008601830270702</v>
+        <v>0.05010500319727119</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1027937938003358</v>
+        <v>-0.1027887129367472</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1079067690787649</v>
+        <v>-0.1078899576384348</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1576066635063939</v>
+        <v>-0.1575977198251302</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0445222059470017</v>
+        <v>-0.04450452763242306</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.195615536410733</v>
+        <v>-0.1956192265491278</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.08900866036056718</v>
+        <v>-0.08896667642065688</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03704826825307921</v>
+        <v>0.03704377403317156</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00800067029933252</v>
+        <v>0.008012779637631709</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.008023240902784261</v>
+        <v>-0.008008709132951744</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09334829065007702</v>
+        <v>0.09335618878759983</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1065094939210832</v>
+        <v>-0.106500198115761</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03638076746577846</v>
+        <v>0.03638214499971695</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.06362663838844781</v>
+        <v>0.06363279463830934</v>
       </c>
     </row>
     <row r="13">
@@ -1426,76 +1431,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09729986073630169</v>
+        <v>0.09729447794028562</v>
       </c>
       <c r="C13" t="n">
-        <v>0.136307629311697</v>
+        <v>0.1363094251330516</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2301923548361527</v>
+        <v>-0.2301907554757129</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3020615274634627</v>
+        <v>0.3020738477862308</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07576258559381105</v>
+        <v>-0.07575694681038168</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2151317993322903</v>
+        <v>0.2151386237058797</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1809675678978812</v>
+        <v>-0.180955477384502</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01292427003830488</v>
+        <v>0.01291673102192414</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3956042339504994</v>
+        <v>-0.3956048494952887</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3268533308202196</v>
+        <v>-0.3268549561522535</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1027937938003358</v>
+        <v>-0.1027887129367472</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06898886587051185</v>
+        <v>0.06898985248184555</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2397109671177216</v>
+        <v>-0.239695491972609</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.04163642938281931</v>
+        <v>-0.04163624186980899</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.06425539045426959</v>
+        <v>-0.06425908281596697</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2227679141734767</v>
+        <v>0.2227737552612175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07347865816498156</v>
+        <v>0.07348923667340836</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03671248794608294</v>
+        <v>0.03670826759140049</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1871850704713914</v>
+        <v>-0.187190729144677</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.264621820608918</v>
+        <v>-0.2646197278766793</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003006152757307705</v>
+        <v>0.002978144109503905</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.100112437185162</v>
+        <v>-0.1001076635200545</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002223203500817146</v>
+        <v>0.002225095864108403</v>
       </c>
     </row>
     <row r="14">
@@ -1505,76 +1510,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1518668796056647</v>
+        <v>-0.151890049394269</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05861628963390444</v>
+        <v>0.05861398777211479</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.01006264811439499</v>
+        <v>-0.01005988316810668</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1878904927738786</v>
+        <v>-0.187892504626183</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1054425165922538</v>
+        <v>-0.1054358383379895</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3374254556157044</v>
+        <v>0.3374241891805202</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04163723932424038</v>
+        <v>0.04163734380550961</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.05564155752038005</v>
+        <v>-0.05566163582415517</v>
       </c>
       <c r="J14" t="n">
-        <v>0.09444000546418722</v>
+        <v>0.09443214469808967</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2044342402161325</v>
+        <v>-0.2044226052390355</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1079067690787649</v>
+        <v>-0.1078899576384348</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06898886587051185</v>
+        <v>0.06898985248184555</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.008933899128898802</v>
+        <v>-0.008926919593707673</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002272557480602841</v>
+        <v>0.002283333592001908</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01609624621768883</v>
+        <v>-0.01610217107701827</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2013998573084214</v>
+        <v>-0.2013770420191938</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1042732297262404</v>
+        <v>-0.1042718866816024</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.08684174763651456</v>
+        <v>-0.08683885171599628</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001835531388863593</v>
+        <v>0.001836453189107313</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2273498002625658</v>
+        <v>-0.2273420153208479</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1136159858105196</v>
+        <v>-0.1136465713016937</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1525410192306047</v>
+        <v>-0.1525347150404998</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.04639860752215329</v>
+        <v>-0.04639707039943974</v>
       </c>
     </row>
     <row r="15">
@@ -1584,76 +1589,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1370001908077368</v>
+        <v>-0.1370110932267852</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0992366786064435</v>
+        <v>-0.09923430316579242</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2534047094186642</v>
+        <v>-0.2534064549677817</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02851201803101562</v>
+        <v>-0.02851547724628593</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1195781180097518</v>
+        <v>-0.1195813813797366</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1658199945466683</v>
+        <v>-0.1658147609980652</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2432501582110838</v>
+        <v>0.2432517924539264</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2298759365661213</v>
+        <v>-0.2298199330257334</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4246943292662151</v>
+        <v>0.4246869187218706</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1075178628469187</v>
+        <v>0.1075175694010564</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1576066635063939</v>
+        <v>-0.1575977198251302</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2397109671177216</v>
+        <v>-0.239695491972609</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.008933899128898802</v>
+        <v>-0.008926919593707673</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.007460272651033347</v>
+        <v>0.00746587005863858</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1476793826393402</v>
+        <v>0.1476748933809305</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.01300083558038435</v>
+        <v>-0.0129855921044267</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1957992953950805</v>
+        <v>-0.1957952209629632</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1428754695771637</v>
+        <v>-0.1428825309577988</v>
       </c>
       <c r="U15" t="n">
-        <v>0.153023660273254</v>
+        <v>0.1530252810814103</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2090725691936517</v>
+        <v>0.2090755592845852</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03608938724647866</v>
+        <v>-0.03610906505577818</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.05738214131450364</v>
+        <v>-0.05737052279547508</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.01154310656126124</v>
+        <v>-0.01154026262825677</v>
       </c>
     </row>
     <row r="16">
@@ -1663,76 +1668,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1127249739367101</v>
+        <v>-0.1127447276196937</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0442752239474057</v>
+        <v>-0.04427799258094919</v>
       </c>
       <c r="D16" t="n">
-        <v>0.008223609492324712</v>
+        <v>0.008226347996079523</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1427816322610606</v>
+        <v>-0.1427839111183754</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06896020041471466</v>
+        <v>-0.06895002916103123</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08146122736654089</v>
+        <v>0.08146038707765331</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0753458375272324</v>
+        <v>0.07534464190533968</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05289203578750189</v>
+        <v>0.05285579173705504</v>
       </c>
       <c r="J16" t="n">
-        <v>0.123211647511375</v>
+        <v>0.1232043876901009</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0128007419277695</v>
+        <v>-0.01278997784750327</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0445222059470017</v>
+        <v>-0.04450452763242306</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.04163642938281931</v>
+        <v>-0.04163624186980899</v>
       </c>
       <c r="N16" t="n">
-        <v>0.002272557480602841</v>
+        <v>0.002283333592001908</v>
       </c>
       <c r="O16" t="n">
-        <v>0.007460272651033347</v>
+        <v>0.00746587005863858</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1500952227945959</v>
+        <v>-0.1501011407559009</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.1420164250252418</v>
+        <v>-0.1419934673521751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2371682630036391</v>
+        <v>-0.2371661901857763</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06866668694153924</v>
+        <v>0.06867143901410709</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1088458490198294</v>
+        <v>-0.1088455605249457</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.115806502575233</v>
+        <v>-0.1158003229314583</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02812738793977011</v>
+        <v>-0.02815650141819007</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.07346997849103136</v>
+        <v>-0.07346733479026839</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.1448414699506264</v>
+        <v>-0.1448385452022492</v>
       </c>
     </row>
     <row r="17">
@@ -1742,76 +1747,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1301134543407329</v>
+        <v>0.1301420301288289</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1363284743839978</v>
+        <v>-0.136338510416104</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2027761353082572</v>
+        <v>-0.2027822939357506</v>
       </c>
       <c r="E17" t="n">
-        <v>0.100999249391847</v>
+        <v>0.1009985120149051</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1689145242965955</v>
+        <v>-0.168918636599317</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02924199543938287</v>
+        <v>0.02923796604566015</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1044094678235964</v>
+        <v>-0.1044111446358953</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09073050659398031</v>
+        <v>-0.09065038121514975</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1014756375578282</v>
+        <v>0.1014743213336673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00179411739675652</v>
+        <v>0.001787335441895209</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.195615536410733</v>
+        <v>-0.1956192265491278</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.06425539045426959</v>
+        <v>-0.06425908281596697</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01609624621768883</v>
+        <v>-0.01610217107701827</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1476793826393402</v>
+        <v>0.1476748933809305</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1500952227945959</v>
+        <v>-0.1501011407559009</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.1516353438547971</v>
+        <v>-0.1516406841661016</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.09855018935151973</v>
+        <v>-0.09855077213585299</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.05067491345127144</v>
+        <v>-0.05068100552677003</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1394812874577067</v>
+        <v>-0.1394888936053489</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1219266449896499</v>
+        <v>0.1219206704775107</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03362241789951845</v>
+        <v>0.03361307764380344</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0848860851615538</v>
+        <v>-0.08489269536228322</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.06080385871291697</v>
+        <v>-0.06080256771045123</v>
       </c>
     </row>
     <row r="18">
@@ -1821,76 +1826,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.08926044237724363</v>
+        <v>-0.08928327343374871</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1769782150924639</v>
+        <v>-0.1769622594398686</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1105162447999311</v>
+        <v>-0.1104974025953657</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1704423847705924</v>
+        <v>0.1704531742841626</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.05169378760910826</v>
+        <v>-0.05165913851231753</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05114826993789341</v>
+        <v>0.05116121844796447</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02157707434981406</v>
+        <v>-0.02157389823051373</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1180822078952703</v>
+        <v>-0.1181941949370826</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1796124706958087</v>
+        <v>-0.1796024334445058</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1376237063138007</v>
+        <v>-0.1375966078458671</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.08900866036056718</v>
+        <v>-0.08896667642065688</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2227679141734767</v>
+        <v>0.2227737552612175</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2013998573084214</v>
+        <v>-0.2013770420191938</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.01300083558038435</v>
+        <v>-0.0129855921044267</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1420164250252418</v>
+        <v>-0.1419934673521751</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1516353438547971</v>
+        <v>-0.1516406841661016</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.004195388652581818</v>
+        <v>-0.004189847874877421</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0570154065617132</v>
+        <v>-0.05699322876063041</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.04530116299188074</v>
+        <v>-0.04528265390821549</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.03681147008693227</v>
+        <v>-0.03679343013023107</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2390419834301527</v>
+        <v>-0.2390442765397111</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3088190537953129</v>
+        <v>0.3088221814895699</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1484276690733499</v>
+        <v>-0.1484192197773317</v>
       </c>
     </row>
     <row r="19">
@@ -1900,76 +1905,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04342727593843259</v>
+        <v>-0.04343917371057757</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1183335022482099</v>
+        <v>-0.1183397601942636</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.04130627747294239</v>
+        <v>-0.04130761654237346</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1147181727134604</v>
+        <v>0.1147158543249246</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07135766496733724</v>
+        <v>0.07136432734008905</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.238209463478683</v>
+        <v>-0.2382071290449189</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06670647932390059</v>
+        <v>0.06670616488106976</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03783608070598626</v>
+        <v>0.03780226506787893</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.05038977099940693</v>
+        <v>-0.05039009457823163</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.09544975381223193</v>
+        <v>-0.09545010646903414</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03704826825307921</v>
+        <v>0.03704377403317156</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07347865816498156</v>
+        <v>0.07348923667340836</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1042732297262404</v>
+        <v>-0.1042718866816024</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1957992953950805</v>
+        <v>-0.1957952209629632</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2371682630036391</v>
+        <v>-0.2371661901857763</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.09855018935151973</v>
+        <v>-0.09855077213585299</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.004195388652581818</v>
+        <v>-0.004189847874877421</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.09024478217155342</v>
+        <v>-0.0902494399184509</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.05397029421884306</v>
+        <v>-0.05396315748873283</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1357656030012703</v>
+        <v>0.1357648490565233</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0472158831786157</v>
+        <v>-0.04721991092008269</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.01342404806028928</v>
+        <v>-0.01341602760063136</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09459197521783237</v>
+        <v>0.09459948244117919</v>
       </c>
     </row>
     <row r="20">
@@ -1979,76 +1984,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01761125922990024</v>
+        <v>0.01761412623434595</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1615178162577572</v>
+        <v>-0.1615079074050299</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07230634013522975</v>
+        <v>0.07228881108610685</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07158893700517846</v>
+        <v>0.07157572414790149</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3523985602249988</v>
+        <v>0.3523852192916541</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.02334607088535038</v>
+        <v>-0.02336016640614961</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1334749252320553</v>
+        <v>-0.1334810332232283</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03356070501395225</v>
+        <v>0.0335619272526978</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2492698718688146</v>
+        <v>-0.2493001100699632</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1737983313306898</v>
+        <v>0.1737964549322871</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00800067029933252</v>
+        <v>0.008012779637631709</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03671248794608294</v>
+        <v>0.03670826759140049</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08684174763651456</v>
+        <v>-0.08683885171599628</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1428754695771637</v>
+        <v>-0.1428825309577988</v>
       </c>
       <c r="P20" t="n">
-        <v>0.06866668694153924</v>
+        <v>0.06867143901410709</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.05067491345127144</v>
+        <v>-0.05068100552677003</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.0570154065617132</v>
+        <v>-0.05699322876063041</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09024478217155342</v>
+        <v>-0.0902494399184509</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1076826352349299</v>
+        <v>-0.10769438199173</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.03168826469833975</v>
+        <v>-0.03169536809865436</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.02695333781032465</v>
+        <v>-0.02698053434314441</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1463043335220386</v>
+        <v>-0.1462995303194226</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1630158226613283</v>
+        <v>-0.1630160588079635</v>
       </c>
     </row>
     <row r="21">
@@ -2058,76 +2063,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.04085644152611399</v>
+        <v>-0.04085686309296784</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2053558100523721</v>
+        <v>-0.205344913828722</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1526331017759159</v>
+        <v>0.1526276934181151</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1484353574178925</v>
+        <v>-0.1484329545327224</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09505737554166228</v>
+        <v>0.0950624669854571</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2337481338195899</v>
+        <v>-0.2337564123759923</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08165012022830004</v>
+        <v>-0.081643276467966</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.08331930945958867</v>
+        <v>-0.08330327777706209</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1604137612389836</v>
+        <v>0.1604078606574873</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09095571445045993</v>
+        <v>0.09095292335246596</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.008023240902784261</v>
+        <v>-0.008008709132951744</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1871850704713914</v>
+        <v>-0.187190729144677</v>
       </c>
       <c r="N21" t="n">
-        <v>0.001835531388863593</v>
+        <v>0.001836453189107313</v>
       </c>
       <c r="O21" t="n">
-        <v>0.153023660273254</v>
+        <v>0.1530252810814103</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1088458490198294</v>
+        <v>-0.1088455605249457</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1394812874577067</v>
+        <v>-0.1394888936053489</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.04530116299188074</v>
+        <v>-0.04528265390821549</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.05397029421884306</v>
+        <v>-0.05396315748873283</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1076826352349299</v>
+        <v>-0.10769438199173</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1498446278670233</v>
+        <v>-0.1498520183714976</v>
       </c>
       <c r="W21" t="n">
-        <v>0.02766881242991233</v>
+        <v>0.0276309182143114</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03667744637522802</v>
+        <v>0.03667322809671286</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.07349716154453906</v>
+        <v>0.07349881134648478</v>
       </c>
     </row>
     <row r="22">
@@ -2137,76 +2142,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1888581676898567</v>
+        <v>-0.188867102039792</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1845230968966702</v>
+        <v>-0.1845197060142055</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.105976736817143</v>
+        <v>-0.1059820257557489</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09317167190127962</v>
+        <v>0.09316943816964515</v>
       </c>
       <c r="F22" t="n">
-        <v>0.118968576666418</v>
+        <v>0.1189671756449346</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3460520810595338</v>
+        <v>-0.3460556248487562</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0913861053480238</v>
+        <v>-0.0913860628590379</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.02216035478439437</v>
+        <v>-0.0221554387693413</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.004585028316468048</v>
+        <v>-0.004598423223231451</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1983526812488879</v>
+        <v>0.1983530599286313</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09334829065007702</v>
+        <v>0.09335618878759983</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.264621820608918</v>
+        <v>-0.2646197278766793</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2273498002625658</v>
+        <v>-0.2273420153208479</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2090725691936517</v>
+        <v>0.2090755592845852</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.115806502575233</v>
+        <v>-0.1158003229314583</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1219266449896499</v>
+        <v>0.1219206704775107</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.03681147008693227</v>
+        <v>-0.03679343013023107</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1357656030012703</v>
+        <v>0.1357648490565233</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.03168826469833975</v>
+        <v>-0.03169536809865436</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1498446278670233</v>
+        <v>-0.1498520183714976</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.06602624531479319</v>
+        <v>-0.06606145969488188</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1512219773257537</v>
+        <v>0.151226355146744</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.09407026857025376</v>
+        <v>-0.09406943421824523</v>
       </c>
     </row>
     <row r="23">
@@ -2216,76 +2221,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.05467102820091285</v>
+        <v>0.0547162421167379</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.01539907032880599</v>
+        <v>-0.01538861344301527</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.06855846166913156</v>
+        <v>-0.06858664143690414</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1759719034724505</v>
+        <v>-0.1759882940074698</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01036291193966002</v>
+        <v>0.0103739633050346</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05793189048947804</v>
+        <v>0.05790932504450037</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.07622998685931839</v>
+        <v>-0.07623953495036964</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06151757704249376</v>
+        <v>0.0615875120513269</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08578769030793169</v>
+        <v>0.08577628200945127</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.01388558215828179</v>
+        <v>-0.01391138176242628</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1065094939210832</v>
+        <v>-0.106500198115761</v>
       </c>
       <c r="M23" t="n">
-        <v>0.003006152757307705</v>
+        <v>0.002978144109503905</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1136159858105196</v>
+        <v>-0.1136465713016937</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.03608938724647866</v>
+        <v>-0.03610906505577818</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.02812738793977011</v>
+        <v>-0.02815650141819007</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.03362241789951845</v>
+        <v>0.03361307764380344</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.2390419834301527</v>
+        <v>-0.2390442765397111</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0472158831786157</v>
+        <v>-0.04721991092008269</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.02695333781032465</v>
+        <v>-0.02698053434314441</v>
       </c>
       <c r="U23" t="n">
-        <v>0.02766881242991233</v>
+        <v>0.0276309182143114</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.06602624531479319</v>
+        <v>-0.06606145969488188</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2393925735328166</v>
+        <v>-0.2394476336733575</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.18656087665865</v>
+        <v>0.1865750039589306</v>
       </c>
     </row>
     <row r="24">
@@ -2295,76 +2300,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007725553553551071</v>
+        <v>0.007719108417908815</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1838508178307589</v>
+        <v>-0.1838604016574403</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2041591103366696</v>
+        <v>-0.2041538565607109</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1550708141127509</v>
+        <v>0.1550830387321695</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00548367558091848</v>
+        <v>0.005500447295324173</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2665605611139177</v>
+        <v>-0.2665557023588059</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2121528262135174</v>
+        <v>-0.2121464427935643</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0380965087930407</v>
+        <v>0.03809097619133221</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04108519734879935</v>
+        <v>0.04108595376632146</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1849044782988844</v>
+        <v>-0.1849012636303527</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03638076746577846</v>
+        <v>0.03638214499971695</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.100112437185162</v>
+        <v>-0.1001076635200545</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1525410192306047</v>
+        <v>-0.1525347150404998</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.05738214131450364</v>
+        <v>-0.05737052279547508</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.07346997849103136</v>
+        <v>-0.07346733479026839</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.0848860851615538</v>
+        <v>-0.08489269536228322</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3088190537953129</v>
+        <v>0.3088221814895699</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.01342404806028928</v>
+        <v>-0.01341602760063136</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1463043335220386</v>
+        <v>-0.1462995303194226</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03667744637522802</v>
+        <v>0.03667322809671286</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1512219773257537</v>
+        <v>0.151226355146744</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.2393925735328166</v>
+        <v>-0.2394476336733575</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.1588635841583275</v>
+        <v>-0.1588621327483982</v>
       </c>
     </row>
     <row r="25">
@@ -2374,73 +2379,73 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1230522628003109</v>
+        <v>0.1229848088942521</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03781351473814417</v>
+        <v>0.03782327476348226</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002591875264624667</v>
+        <v>0.002594116113053682</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3926531288297701</v>
+        <v>-0.392647984146043</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1604492106734625</v>
+        <v>0.1604558452863722</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0122884121285944</v>
+        <v>-0.0122854438104707</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1278732479702974</v>
+        <v>-0.12786554682743</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2242213227618077</v>
+        <v>-0.2241990516037803</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.06856156683471989</v>
+        <v>-0.06855543635369574</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.03808703406425892</v>
+        <v>-0.03808508483684496</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06362663838844781</v>
+        <v>0.06363279463830934</v>
       </c>
       <c r="M25" t="n">
-        <v>0.002223203500817146</v>
+        <v>0.002225095864108403</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.04639860752215329</v>
+        <v>-0.04639707039943974</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.01154310656126124</v>
+        <v>-0.01154026262825677</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1448414699506264</v>
+        <v>-0.1448385452022492</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.06080385871291697</v>
+        <v>-0.06080256771045123</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1484276690733499</v>
+        <v>-0.1484192197773317</v>
       </c>
       <c r="S25" t="n">
-        <v>0.09459197521783237</v>
+        <v>0.09459948244117919</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1630158226613283</v>
+        <v>-0.1630160588079635</v>
       </c>
       <c r="U25" t="n">
-        <v>0.07349716154453906</v>
+        <v>0.07349881134648478</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.09407026857025376</v>
+        <v>-0.09406943421824523</v>
       </c>
       <c r="W25" t="n">
-        <v>0.18656087665865</v>
+        <v>0.1865750039589306</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1588635841583275</v>
+        <v>-0.1588621327483982</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
